--- a/Backend/expense_details.xlsx
+++ b/Backend/expense_details.xlsx
@@ -397,44 +397,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Catagory</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Amount</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Date</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>rent</v>
-      </c>
-      <c r="B2">
-        <v>400</v>
-      </c>
-      <c r="C2" t="str">
-        <v>2025-12-01</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>rent</v>
-      </c>
-      <c r="B3">
-        <v>500</v>
-      </c>
-      <c r="C3" t="str">
-        <v>2025-12-01</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetData/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Backend/expense_details.xlsx
+++ b/Backend/expense_details.xlsx
@@ -397,10 +397,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:C3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Catagory</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Amount</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Date</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>food</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026-02-22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>cloths</v>
+      </c>
+      <c r="B3">
+        <v>600</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026-02-21</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Backend/expense_details.xlsx
+++ b/Backend/expense_details.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -412,13 +412,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>food</v>
+        <v>gift</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>167</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
     </row>
     <row r="3">
@@ -426,15 +426,48 @@
         <v>cloths</v>
       </c>
       <c r="B3">
-        <v>600</v>
+        <v>10</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-02-21</v>
+        <v>2026-02-18</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Rent</v>
+      </c>
+      <c r="B4">
+        <v>40</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026-02-17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>food</v>
+      </c>
+      <c r="B5">
+        <v>20</v>
+      </c>
+      <c r="C5" t="str">
+        <v>2026-02-13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Omid AFG</v>
+      </c>
+      <c r="B6">
+        <v>100</v>
+      </c>
+      <c r="C6" t="str">
+        <v>2026-02-13</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>